--- a/小野町_引継ぎ_整理済/21_給付適正化・交付金/小野町_給付適正化と交付金_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/21_給付適正化・交付金/小野町_給付適正化と交付金_20260928.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>令和8年度交付金は537点／800点です。全国平均454.8点を82点上回り、全国258位／1,536、県内13位／59です。令和6年度は233点（全国平均の55％）でしたから、2年で全国平均を上回るところまで来ています（第2章）</t>
+          <t>令和8年度交付金は537点／800点です。市町村分の平均454.8点を82点上回り、市町村分1,536保険者のうち258位、県内13位／59です。令和6年度は233点（当時の平均の55％）でしたから、2年で平均を上回るところまで来ています。ただし受領したのは市町村分だけで、公表順位の母数は広域連合を含む1,741保険者です。上の258位は公表順位ではありません（第2章1）</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>介護給付適正化は弱点ではなく強みです。推進交付金の目標Ⅱは84点で、全国平均69.1点を上回ります。体制・取組の68点は配点満点です（満点は全国392保険者／1,536、県内11／59）（第3章）</t>
+          <t>介護給付適正化は弱点ではなく強みです。推進交付金の目標Ⅱは84点で、全国平均69.1点を上回ります。体制・取組の68点は配点満点です（満点は市町村分392保険者／1,536、県内11／59）（第3章）</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>医療情報との突合は16点＝配点満点（全保険者の上位1割）です。0点なのはケアプラン点検の実施割合（配点16点）だけです。主要3事業はいずれも実施しているものとして計上されています（第3章）</t>
+          <t>医療情報との突合は16点＝配点満点（全保険者の上位1割）です。0点なのはケアプラン点検の実施割合（配点16点）だけです。主要3事業は、該当状況調査に対する町の回答では3事業すべてを実施（予定を含む）として計上されています。実施の内容（点検件数・委託の有無）は確認中です（第3章2）</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>この68点は計画の記載に支えられています。給付費適正化方策の策定状況（配点32点）は、方策の策定・評価指標の設定・毎年度の見直し・成果の公表の4つを問うもので、第10期計画に同じ水準の記載を置かなければ失点します（第3章3）</t>
+          <t>この68点の根拠となっている文書が確認できていません。給付費適正化方策の策定状況（配点32点）は、方策の策定・評価指標の設定・毎年度の見直し・成果の公表の4つを問うものですが、第9期計画本文には主要3事業の記載はあるものの、効果を検証するための評価指標も毎年度の定量的な目標もありません。別の文書で定めているのか、回答のみなのかを確かめたうえで、第10期計画に明示する必要があります（第3章3）</t>
         </is>
       </c>
     </row>
@@ -652,6 +652,34 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>給付適正化計画の位置づけを決めていただく必要があります。当方は案B（第4章 基本目標3①の中に主要3事業の毎年度の定量的な目標を掲げる）をお勧めします（第7章1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>※</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>本書の「全国順位」「全国平均」「全国該当率」は、受領した市町村分の集計表（1,536保険者）の中での値です。広域連合分は別表であり受領していません。国の公表順位の母数は広域連合を含む1,741保険者で、小野町の令和7年度は表内1,339位に対し公表1,513位でした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>※</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>体制・取組と活動の600点は、該当状況調査に対する保険者の回答を集計したものです（成果指標群200点のみ国が介護DB・NDBから算定）。実施内容の監査を経た数値ではありません。</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6705,7 +6733,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>合計（重複を含む）</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -6717,6 +6745,44 @@
       </c>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>※ 成果指標群（目標Ⅳ）のア系とイ系は択一で、「アとイを比較し、より上位となった方で得点」する。健康寿命延伸のア①とイ①はどちらか一方しか取れないため、上の合計は5点分の重複を含む。</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>※ 配点は、枝番の列の最大値。「全国該当率」は市町村分の中で得点している保険者の割合。</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7297,12 +7363,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>実施（調査票の回答による）</t>
+          <t>実施（調査票の回答）</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>指標2アで「3事業の全てを実施している」として6点を得点しています。実施の内容（点検件数・委託の有無）を確かめる必要があります</t>
+          <t>指標2アで「3事業の全てを実施している」として6点を得点しています。同指標は令和7年度の実施（予定を含む）の状況を問うもので、実施の内容（点検件数・委託の有無）は確かめられていません</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7385,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>実施。ただし実施割合は全保険者の下位3割</t>
+          <t>実施（調査票の回答）。ただし令和6年度の実施割合は全保険者の上位7割に入っていない</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>体制・取組では得点していますが、活動指標群の「ケアプラン点検の実施割合」は0点（配点16点）です</t>
+          <t>体制・取組では得点していますが、活動指標群の「ケアプラン点検の実施割合」は0点（配点16点）です。件数が少ないのか、報告していないのかは確かめられていません</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7407,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>実施。突合の実施割合は全保険者の上位1割</t>
+          <t>実施。令和6年度の突合の実施割合は全保険者の上位1割</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>活動指標群の「医療情報との突合の実施状況」は16点＝配点満点です。縦覧点検も4帳票すべてを点検しています</t>
+          <t>活動指標群の「医療情報との突合の実施状況」は16点＝配点満点です。縦覧点検も4帳票すべてを点検しているとの回答です。国保連への委託の有無は評価指標からは分かりません</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7658,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>令和7年度の実績（住宅改修 年22件）を基礎に設定できる</t>
+          <t>令和7年度の実績（住宅改修 年33件＝介護22・予防11）を基礎に設定できる</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7691,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>同（特定福祉用具販売 年45件）</t>
+          <t>同（特定福祉用具販売 年62件＝介護45・予防17）</t>
         </is>
       </c>
     </row>
